--- a/eval/dataset/files/measurements.xlsx
+++ b/eval/dataset/files/measurements.xlsx
@@ -125,6 +125,151 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>V-I characteristic (R=250 ohm)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'V-I Readings'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'V-I Readings'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'V-I Readings'!$B$2:$B$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>voltage_V</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>current_mA</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -480,6 +625,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/eval/dataset/files/measurements.xlsx
+++ b/eval/dataset/files/measurements.xlsx
@@ -169,12 +169,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'V-I Readings'!$A$2:$A$5</f>
+              <f>'V-I Readings'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'V-I Readings'!$B$2:$B$5</f>
+              <f>'V-I Readings'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,10 +581,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>250</v>
@@ -592,10 +592,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B3" t="n">
         <v>6</v>
-      </c>
-      <c r="B3" t="n">
-        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>250</v>
@@ -603,10 +603,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>250</v>
@@ -614,12 +614,221 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
         <v>12</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C6" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C9" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C11" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C12" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B13" t="n">
+        <v>26</v>
+      </c>
+      <c r="C13" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" t="n">
+        <v>28</v>
+      </c>
+      <c r="C14" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>34</v>
+      </c>
+      <c r="C17" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" t="n">
+        <v>36</v>
+      </c>
+      <c r="C18" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="B19" t="n">
+        <v>38</v>
+      </c>
+      <c r="C19" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" t="n">
+        <v>40</v>
+      </c>
+      <c r="C20" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>42</v>
+      </c>
+      <c r="C21" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" t="n">
+        <v>44</v>
+      </c>
+      <c r="C22" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="B23" t="n">
+        <v>46</v>
+      </c>
+      <c r="C23" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B24" t="n">
         <v>48</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C24" t="n">
         <v>250</v>
       </c>
     </row>
